--- a/Datos/CSV2.xlsx
+++ b/Datos/CSV2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sedima0.sharepoint.com/sites/SharePoint/Documentos compartidos/Archivos Tecnicos/3. Proyectos/DEMO GLV/Sedima_Visor/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{54E57868-2AA4-4AA8-96BD-009519BE5D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52D11F7A-2A08-41B5-8D98-EFC9D4216EF4}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{54E57868-2AA4-4AA8-96BD-009519BE5D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B50AEAA-AF9B-4086-A446-B1983E02EFB2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D45AEAEA-F73E-4F99-97FD-08996ABE9081}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>TAG</t>
   </si>
@@ -90,6 +90,27 @@
   </si>
   <si>
     <t>terminado</t>
+  </si>
+  <si>
+    <t>REG-401</t>
+  </si>
+  <si>
+    <t>Revisión</t>
+  </si>
+  <si>
+    <t>PIT-501</t>
+  </si>
+  <si>
+    <t>Mecanico</t>
+  </si>
+  <si>
+    <t>Terminado</t>
+  </si>
+  <si>
+    <t>FE-323</t>
+  </si>
+  <si>
+    <t>Jarenas</t>
   </si>
 </sst>
 </file>
@@ -162,7 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -171,6 +192,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -218,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{087EF8F4-EB3B-4F85-A6AF-E1350A58E67A}" name="MANTTO" displayName="MANTTO" ref="A1:F4" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F4" xr:uid="{087EF8F4-EB3B-4F85-A6AF-E1350A58E67A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{087EF8F4-EB3B-4F85-A6AF-E1350A58E67A}" name="MANTTO" displayName="MANTTO" ref="A1:F7" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:F7" xr:uid="{087EF8F4-EB3B-4F85-A6AF-E1350A58E67A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0910DDF2-3F64-4E71-8144-1F88F8098F92}" name="TAG"/>
     <tableColumn id="2" xr3:uid="{6FDC1D3B-6266-4CBD-8ECE-54B2F213E074}" name="FECHA"/>
@@ -549,13 +571,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F781B83-06C9-454D-852D-4C8E1A76502A}">
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="4"/>
+    <col min="6" max="6" width="12.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -596,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="3">
-        <v>1000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -616,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="3">
-        <v>2000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -636,14 +658,77 @@
         <v>17</v>
       </c>
       <c r="F4" s="3">
-        <v>5000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15">
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45882</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45881</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45882</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="15">
-      <c r="F15" s="5"/>
+    <row r="15" spans="1:12"/>
+    <row r="16" spans="1:12"/>
+    <row r="17" spans="6:6"/>
+    <row r="18" spans="6:6" ht="15" customHeight="1">
+      <c r="F18" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -654,15 +739,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008179FB738B52054CB49D1EA14F3B017D" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf92993d4be1ca8d869739abdcab03f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="38982260-ffbb-4d45-bf74-3f340fef217a" xmlns:ns3="4beaf995-bca9-4e52-9e7c-0ff6540365ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="306cbce10ee737f78145650a7152b8c6" ns2:_="" ns3:_="">
     <xsd:import namespace="38982260-ffbb-4d45-bf74-3f340fef217a"/>
@@ -857,7 +933,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="4beaf995-bca9-4e52-9e7c-0ff6540365ad" xsi:nil="true"/>
@@ -868,14 +944,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB99B906-73A9-4854-848A-306366E9CF00}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{696D3610-C100-4EA6-87B9-ECA94F4786AA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9E9234B-7E01-463C-B8D7-873971FDD765}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB99B906-73A9-4854-848A-306366E9CF00}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{696D3610-C100-4EA6-87B9-ECA94F4786AA}"/>
 </file>
--- a/Datos/CSV2.xlsx
+++ b/Datos/CSV2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sedima0.sharepoint.com/sites/SharePoint/Documentos compartidos/Archivos Tecnicos/3. Proyectos/DEMO GLV/Sedima_Visor/Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1463" documentId="8_{54E57868-2AA4-4AA8-96BD-009519BE5D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC636E9B-E581-472F-BAC1-9BE0C4B5F088}"/>
+  <xr:revisionPtr revIDLastSave="1464" documentId="8_{54E57868-2AA4-4AA8-96BD-009519BE5D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB339AE-D286-4ECF-86EF-160F16E3442A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D45AEAEA-F73E-4F99-97FD-08996ABE9081}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4022" r:id="rId3"/>
-    <pivotCache cacheId="4040" r:id="rId4"/>
+    <pivotCache cacheId="5493" r:id="rId3"/>
+    <pivotCache cacheId="5497" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -538,12 +538,6 @@
     <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -560,6 +554,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -7998,8 +7998,8 @@
       <xdr:rowOff>329499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>2486765</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>762740</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>68889</xdr:rowOff>
     </xdr:to>
@@ -8187,56 +8187,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Excel Services" refreshedDate="45890.707049421297" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{667D8D1C-85AF-4D7B-9B5D-C4C32941DFB8}">
-  <cacheSource type="worksheet">
-    <worksheetSource name="MANTTO"/>
-  </cacheSource>
-  <cacheFields count="9">
-    <cacheField name="TAG" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="FECHA" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-08-06T00:00:00" maxDate="2025-08-23T00:00:00"/>
-    </cacheField>
-    <cacheField name="ACTIVIDAD" numFmtId="0">
-      <sharedItems count="6">
-        <s v="Lubricación"/>
-        <s v="Inspección "/>
-        <s v="Limpieza y ajuste"/>
-        <s v="Pruebas de señal"/>
-        <s v="Calibración"/>
-        <s v="Medición de espesores"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="TIEMPO INACTIVIDAD O DURACIÓN DEL EVENTO (min)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="100"/>
-    </cacheField>
-    <cacheField name="TIPO DE MANTENIMIENTO" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="RESPONSABLE" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="RESULTADO" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0.375" maxValue="0.375"/>
-    </cacheField>
-    <cacheField name="COSTO" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="509800"/>
-    </cacheField>
-    <cacheField name="OBSERVACIONES" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Excel Services" refreshedDate="45890.707773032409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{3BD00387-F3CF-485E-A236-2341BA471B80}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Excel Services" refreshedDate="45891.396672222225" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{3BD00387-F3CF-485E-A236-2341BA471B80}">
   <cacheSource type="worksheet">
     <worksheetSource name="MANTTO"/>
   </cacheSource>
@@ -8298,144 +8249,56 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
-  <r>
-    <s v="VAL-101"/>
-    <d v="2025-08-11T00:00:00"/>
-    <x v="0"/>
-    <n v="90"/>
-    <s v="Preventivo"/>
-    <s v="Tecnico"/>
-    <s v="Satisfactorio"/>
-    <n v="200000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="VAL-102"/>
-    <d v="2025-08-06T00:00:00"/>
-    <x v="1"/>
-    <n v="100"/>
-    <s v="Preventivo"/>
-    <s v="Mecanico"/>
-    <s v="Satisfactorio"/>
-    <n v="200000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="VAL-108"/>
-    <d v="2025-08-11T00:00:00"/>
-    <x v="2"/>
-    <n v="60"/>
-    <s v="correctivo"/>
-    <s v="operador"/>
-    <s v="terminado"/>
-    <n v="500000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="REG-401"/>
-    <d v="2025-08-13T00:00:00"/>
-    <x v="3"/>
-    <n v="90"/>
-    <s v="correctivo"/>
-    <s v="Tecnico"/>
-    <s v="Satisfactorio"/>
-    <n v="150000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="PIT-501"/>
-    <d v="2025-08-12T00:00:00"/>
-    <x v="4"/>
-    <n v="50"/>
-    <s v="avería"/>
-    <s v="Mecanico"/>
-    <s v="terminado"/>
-    <n v="120000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="FET-456"/>
-    <d v="2025-08-13T00:00:00"/>
-    <x v="0"/>
-    <n v="90"/>
-    <s v="Preventivo"/>
-    <s v="Tecnico"/>
-    <s v="terminado"/>
-    <n v="500000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="VAL-101"/>
-    <d v="2025-08-20T00:00:00"/>
-    <x v="2"/>
-    <n v="60"/>
-    <s v="Preventivo"/>
-    <s v="operador"/>
-    <s v="terminado"/>
-    <n v="400000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="PI-102"/>
-    <d v="2025-08-22T00:00:00"/>
-    <x v="4"/>
-    <n v="90"/>
-    <s v="Preventivo"/>
-    <s v="Mecanico"/>
-    <s v="Satisfactorio"/>
-    <n v="400000"/>
-    <s v="Sin novedad"/>
-  </r>
-  <r>
-    <s v="REG-201"/>
-    <d v="2025-08-19T00:00:00"/>
-    <x v="3"/>
-    <n v="100"/>
-    <s v="correctivo"/>
-    <s v="Tecnico"/>
-    <s v="terminado"/>
-    <n v="509800"/>
-    <s v="Regulador en funcionamiento correcto"/>
-  </r>
-  <r>
-    <s v="VAL-114"/>
-    <d v="2025-08-19T00:00:00"/>
-    <x v="0"/>
-    <n v="90"/>
-    <s v="Preventivo"/>
-    <s v="Tecnico"/>
-    <s v="terminado"/>
-    <n v="398760"/>
-    <s v="Valvula en funcionamiento"/>
-  </r>
-  <r>
-    <s v="TUB-990"/>
-    <d v="2025-08-14T00:00:00"/>
-    <x v="5"/>
-    <n v="5"/>
-    <s v="Preventivo"/>
-    <s v="Apellido"/>
-    <n v="0.375"/>
-    <n v="0"/>
-    <s v="N/A."/>
-  </r>
-  <r>
-    <s v="VAL-101"/>
-    <d v="2025-08-20T00:00:00"/>
-    <x v="0"/>
-    <n v="90"/>
-    <s v="Preventivo"/>
-    <s v="Tecnico"/>
-    <s v="Satisfactorio"/>
-    <n v="490876"/>
-    <s v="Sin novedad"/>
-  </r>
-</pivotCacheRecords>
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Excel Services" refreshedDate="45891.396672453702" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{667D8D1C-85AF-4D7B-9B5D-C4C32941DFB8}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="MANTTO"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="TAG" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="FECHA" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-08-06T00:00:00" maxDate="2025-08-23T00:00:00"/>
+    </cacheField>
+    <cacheField name="ACTIVIDAD" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Lubricación"/>
+        <s v="Inspección "/>
+        <s v="Limpieza y ajuste"/>
+        <s v="Pruebas de señal"/>
+        <s v="Calibración"/>
+        <s v="Medición de espesores"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TIEMPO INACTIVIDAD O DURACIÓN DEL EVENTO (min)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="100"/>
+    </cacheField>
+    <cacheField name="TIPO DE MANTENIMIENTO" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="RESPONSABLE" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="RESULTADO" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="COSTO" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="509800"/>
+    </cacheField>
+    <cacheField name="OBSERVACIONES" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
   <r>
     <s v="VAL-101"/>
@@ -8572,8 +8435,145 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <s v="VAL-101"/>
+    <d v="2025-08-11T00:00:00"/>
+    <x v="0"/>
+    <n v="90"/>
+    <s v="Preventivo"/>
+    <s v="Tecnico"/>
+    <s v="Satisfactorio"/>
+    <n v="200000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="VAL-102"/>
+    <d v="2025-08-06T00:00:00"/>
+    <x v="1"/>
+    <n v="100"/>
+    <s v="Preventivo"/>
+    <s v="Mecanico"/>
+    <s v="Satisfactorio"/>
+    <n v="200000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="VAL-108"/>
+    <d v="2025-08-11T00:00:00"/>
+    <x v="2"/>
+    <n v="60"/>
+    <s v="correctivo"/>
+    <s v="operador"/>
+    <s v="terminado"/>
+    <n v="500000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="REG-401"/>
+    <d v="2025-08-13T00:00:00"/>
+    <x v="3"/>
+    <n v="90"/>
+    <s v="correctivo"/>
+    <s v="Tecnico"/>
+    <s v="Satisfactorio"/>
+    <n v="150000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="PIT-501"/>
+    <d v="2025-08-12T00:00:00"/>
+    <x v="4"/>
+    <n v="50"/>
+    <s v="avería"/>
+    <s v="Mecanico"/>
+    <s v="terminado"/>
+    <n v="120000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="FET-456"/>
+    <d v="2025-08-13T00:00:00"/>
+    <x v="0"/>
+    <n v="90"/>
+    <s v="Preventivo"/>
+    <s v="Tecnico"/>
+    <s v="terminado"/>
+    <n v="500000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="VAL-101"/>
+    <d v="2025-08-20T00:00:00"/>
+    <x v="2"/>
+    <n v="60"/>
+    <s v="Preventivo"/>
+    <s v="operador"/>
+    <s v="terminado"/>
+    <n v="400000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="PI-102"/>
+    <d v="2025-08-22T00:00:00"/>
+    <x v="4"/>
+    <n v="90"/>
+    <s v="Preventivo"/>
+    <s v="Mecanico"/>
+    <s v="Satisfactorio"/>
+    <n v="400000"/>
+    <s v="Sin novedad"/>
+  </r>
+  <r>
+    <s v="REG-201"/>
+    <d v="2025-08-19T00:00:00"/>
+    <x v="3"/>
+    <n v="100"/>
+    <s v="correctivo"/>
+    <s v="Tecnico"/>
+    <s v="terminado"/>
+    <n v="509800"/>
+    <s v="Regulador en funcionamiento correcto"/>
+  </r>
+  <r>
+    <s v="VAL-114"/>
+    <d v="2025-08-19T00:00:00"/>
+    <x v="0"/>
+    <n v="90"/>
+    <s v="Preventivo"/>
+    <s v="Tecnico"/>
+    <s v="terminado"/>
+    <n v="398760"/>
+    <s v="Valvula en funcionamiento"/>
+  </r>
+  <r>
+    <s v="TUB-990"/>
+    <d v="2025-08-14T00:00:00"/>
+    <x v="5"/>
+    <n v="5"/>
+    <s v="Preventivo"/>
+    <s v="Tecnico"/>
+    <s v="terminado"/>
+    <n v="0"/>
+    <s v="N/A."/>
+  </r>
+  <r>
+    <s v="VAL-101"/>
+    <d v="2025-08-20T00:00:00"/>
+    <x v="0"/>
+    <n v="90"/>
+    <s v="Preventivo"/>
+    <s v="Tecnico"/>
+    <s v="Satisfactorio"/>
+    <n v="490876"/>
+    <s v="Sin novedad"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08DA80D9-75AD-4824-AB69-12478CA9E8B5}" name="TablaDinámica9" cacheId="4040" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21" rowHeaderCaption="Responsable">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08DA80D9-75AD-4824-AB69-12478CA9E8B5}" name="TablaDinámica9" cacheId="5493" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21" rowHeaderCaption="Responsable">
   <location ref="N26:O30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -8905,7 +8905,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25BF5F57-315A-4EA3-A25E-4BB37674F347}" name="TablaDinámica2" cacheId="4022" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Actividad">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25BF5F57-315A-4EA3-A25E-4BB37674F347}" name="TablaDinámica2" cacheId="5497" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Actividad">
   <location ref="N17:O24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -9173,7 +9173,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A330C77E-3D0D-4EC2-AED0-B3C0EAC051F6}" name="TablaDinámica12" cacheId="4040" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Actividad">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A330C77E-3D0D-4EC2-AED0-B3C0EAC051F6}" name="TablaDinámica12" cacheId="5493" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Actividad">
   <location ref="N47:O54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -9355,7 +9355,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D07F0731-FC58-4F5F-AF9F-7F5ECF5D6B56}" name="TablaDinámica11" cacheId="4040" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Resultado">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D07F0731-FC58-4F5F-AF9F-7F5ECF5D6B56}" name="TablaDinámica11" cacheId="5493" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Resultado">
   <location ref="N41:O44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -9549,7 +9549,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{677A784E-F652-4403-8C1F-4899EAC79059}" name="TablaDinámica10" cacheId="4040" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Tipo Mantenimiento">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{677A784E-F652-4403-8C1F-4899EAC79059}" name="TablaDinámica10" cacheId="5493" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Tipo Mantenimiento">
   <location ref="N34:O38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -10529,8 +10529,8 @@
     <col min="11" max="11" width="96.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="40" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="52.140625" customWidth="1"/>
-    <col min="14" max="14" width="50.28515625" customWidth="1"/>
-    <col min="15" max="15" width="52.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="43.7109375" customWidth="1"/>
+    <col min="15" max="15" width="32.42578125" style="24" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="43" style="24" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="11.5703125" customWidth="1"/>
     <col min="19" max="19" width="11.5703125" style="21" customWidth="1"/>
@@ -10573,7 +10573,7 @@
     </row>
     <row r="7" spans="4:18" ht="26.25">
       <c r="D7" s="19"/>
-      <c r="J7" s="43"/>
+      <c r="J7" s="41"/>
       <c r="R7" s="13"/>
     </row>
     <row r="8" spans="4:18">
@@ -10610,19 +10610,19 @@
     </row>
     <row r="13" spans="4:18" ht="63.75">
       <c r="D13" s="19"/>
-      <c r="H13" s="39">
+      <c r="H13" s="37">
         <f>COUNTA(MANTTO[TAG])</f>
         <v>12</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13" s="36">
         <f>SUM(MANTTO[COSTO])</f>
         <v>3869436</v>
       </c>
-      <c r="M13" s="39">
+      <c r="M13" s="37">
         <f>AVERAGE(MANTTO[TIEMPO INACTIVIDAD O DURACIÓN DEL EVENTO (min)])</f>
         <v>76.25</v>
       </c>
-      <c r="O13" s="40">
+      <c r="O13" s="38">
         <f>COUNTIF(MANTTO[RESULTADO],"Satisfactorio")/COUNTA(MANTTO[RESULTADO])</f>
         <v>0.41666666666666669</v>
       </c>
@@ -10741,7 +10741,7 @@
       <c r="N27" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="O27" s="36">
+      <c r="O27" s="42">
         <v>3</v>
       </c>
       <c r="R27" s="13"/>
@@ -10751,7 +10751,7 @@
       <c r="N28" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="O28" s="36">
+      <c r="O28" s="42">
         <v>2</v>
       </c>
       <c r="R28" s="13"/>
@@ -10761,7 +10761,7 @@
       <c r="N29" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="O29" s="36">
+      <c r="O29" s="42">
         <v>7</v>
       </c>
       <c r="R29" s="13"/>
@@ -10771,7 +10771,7 @@
       <c r="N30" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="O30" s="37">
+      <c r="O30" s="43">
         <v>12</v>
       </c>
       <c r="R30" s="13"/>
@@ -10808,7 +10808,7 @@
       <c r="N35" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="42">
         <v>1</v>
       </c>
       <c r="R35" s="13"/>
@@ -10818,7 +10818,7 @@
       <c r="N36" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="42">
         <v>3</v>
       </c>
       <c r="R36" s="13"/>
@@ -10828,7 +10828,7 @@
       <c r="N37" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="O37" s="36">
+      <c r="O37" s="42">
         <v>8</v>
       </c>
       <c r="R37" s="13"/>
@@ -10838,7 +10838,7 @@
       <c r="N38" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="O38" s="37">
+      <c r="O38" s="43">
         <v>12</v>
       </c>
       <c r="R38" s="13"/>
@@ -10870,7 +10870,7 @@
       <c r="N42" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="O42" s="36">
+      <c r="O42" s="42">
         <v>5</v>
       </c>
       <c r="R42" s="13"/>
@@ -10880,7 +10880,7 @@
       <c r="N43" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="O43" s="36">
+      <c r="O43" s="42">
         <v>7</v>
       </c>
       <c r="R43" s="13"/>
@@ -10890,7 +10890,7 @@
       <c r="N44" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="O44" s="37">
+      <c r="O44" s="43">
         <v>12</v>
       </c>
       <c r="R44" s="13"/>
@@ -10908,10 +10908,10 @@
     </row>
     <row r="47" spans="4:18" ht="60">
       <c r="D47" s="19"/>
-      <c r="N47" s="42" t="s">
+      <c r="N47" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="O47" s="41" t="s">
+      <c r="O47" s="39" t="s">
         <v>53</v>
       </c>
       <c r="R47" s="13"/>
@@ -10921,7 +10921,7 @@
       <c r="N48" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="O48" s="36">
+      <c r="O48" s="42">
         <v>70</v>
       </c>
       <c r="R48" s="13"/>
@@ -10931,7 +10931,7 @@
       <c r="N49" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="O49" s="36">
+      <c r="O49" s="42">
         <v>100</v>
       </c>
       <c r="R49" s="13"/>
@@ -10941,7 +10941,7 @@
       <c r="N50" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="O50" s="36">
+      <c r="O50" s="42">
         <v>60</v>
       </c>
       <c r="R50" s="13"/>
@@ -10951,7 +10951,7 @@
       <c r="N51" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="O51" s="36">
+      <c r="O51" s="42">
         <v>90</v>
       </c>
       <c r="R51" s="13"/>
@@ -10961,7 +10961,7 @@
       <c r="N52" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="O52" s="36">
+      <c r="O52" s="42">
         <v>95</v>
       </c>
       <c r="R52" s="13"/>
@@ -10971,7 +10971,7 @@
       <c r="N53" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="O53" s="36">
+      <c r="O53" s="42">
         <v>5</v>
       </c>
       <c r="R53" s="13"/>
@@ -10981,7 +10981,7 @@
       <c r="N54" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="O54" s="37">
+      <c r="O54" s="43">
         <v>76.25</v>
       </c>
       <c r="R54" s="13"/>
@@ -11016,7 +11016,7 @@
     </row>
     <row r="62" spans="4:18" ht="26.25">
       <c r="D62" s="19"/>
-      <c r="N62" s="43"/>
+      <c r="N62" s="41"/>
       <c r="R62" s="13"/>
     </row>
     <row r="63" spans="4:18">
@@ -11087,26 +11087,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="4beaf995-bca9-4e52-9e7c-0ff6540365ad" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="38982260-ffbb-4d45-bf74-3f340fef217a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008179FB738B52054CB49D1EA14F3B017D" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf92993d4be1ca8d869739abdcab03f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="38982260-ffbb-4d45-bf74-3f340fef217a" xmlns:ns3="4beaf995-bca9-4e52-9e7c-0ff6540365ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="306cbce10ee737f78145650a7152b8c6" ns2:_="" ns3:_="">
     <xsd:import namespace="38982260-ffbb-4d45-bf74-3f340fef217a"/>
@@ -11301,8 +11281,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="4beaf995-bca9-4e52-9e7c-0ff6540365ad" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="38982260-ffbb-4d45-bf74-3f340fef217a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{696D3610-C100-4EA6-87B9-ECA94F4786AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB99B906-73A9-4854-848A-306366E9CF00}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11310,5 +11310,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB99B906-73A9-4854-848A-306366E9CF00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{696D3610-C100-4EA6-87B9-ECA94F4786AA}"/>
 </file>